--- a/sheets/조재수대금교본/검수/약속.xlsx
+++ b/sheets/조재수대금교본/검수/약속.xlsx
@@ -3250,23 +3250,11 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -3423,8 +3411,7 @@
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -3437,8 +3424,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -3509,29 +3495,13 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
     <row r="11" ht="75.27" customHeight="true">
@@ -3634,11 +3604,7 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/약속.xlsx
+++ b/sheets/조재수대금교본/검수/약속.xlsx
@@ -3411,7 +3411,8 @@
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -3424,7 +3425,8 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="M8" s="24"/>

--- a/sheets/조재수대금교본/검수/약속.xlsx
+++ b/sheets/조재수대금교본/검수/약속.xlsx
@@ -3149,26 +3149,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="50.63" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="75.27" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="75.27" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="75.27" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="75.27" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="75.27" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3386,7 +3386,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="75.27" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="75.27" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="75.27" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3506,7 +3506,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="75.27" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="75.27" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="75.27" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="75.27" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3686,6 +3686,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="79"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>